--- a/final_data_pipeline/output/312140_elec_options.xlsx
+++ b/final_data_pipeline/output/312140_elec_options.xlsx
@@ -831,7 +831,7 @@
         <v>82</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -926,7 +926,7 @@
         <v>82</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -1021,7 +1021,7 @@
         <v>82</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1119,7 +1119,7 @@
         <v>82</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -1214,7 +1214,7 @@
         <v>82</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE6">
         <v>8000</v>
@@ -1309,7 +1309,7 @@
         <v>82</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE7">
         <v>8000</v>
@@ -2550,7 +2550,7 @@
         <v>82</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE20">
         <v>8000</v>
@@ -2645,7 +2645,7 @@
         <v>82</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE21">
         <v>8000</v>
@@ -2740,7 +2740,7 @@
         <v>82</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE22">
         <v>8000</v>
@@ -2835,7 +2835,7 @@
         <v>82</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE23">
         <v>8000</v>
@@ -2933,7 +2933,7 @@
         <v>82</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE24">
         <v>8000</v>
@@ -3028,7 +3028,7 @@
         <v>82</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE25">
         <v>8000</v>
@@ -3126,7 +3126,7 @@
         <v>82</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE26">
         <v>8000</v>
@@ -3221,7 +3221,7 @@
         <v>82</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE27">
         <v>8000</v>
@@ -3316,7 +3316,7 @@
         <v>82</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE28">
         <v>8000</v>
@@ -3411,7 +3411,7 @@
         <v>82</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE29">
         <v>8000</v>
@@ -3506,7 +3506,7 @@
         <v>82</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE30">
         <v>8000</v>
@@ -3601,7 +3601,7 @@
         <v>82</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE31">
         <v>8000</v>
@@ -3696,7 +3696,7 @@
         <v>82</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE32">
         <v>8000</v>
@@ -3791,7 +3791,7 @@
         <v>82</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE33">
         <v>8000</v>
@@ -3886,7 +3886,7 @@
         <v>82</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE34">
         <v>8000</v>
@@ -3981,7 +3981,7 @@
         <v>82</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE35">
         <v>8000</v>
@@ -4079,7 +4079,7 @@
         <v>82</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE36">
         <v>8000</v>
@@ -4174,7 +4174,7 @@
         <v>82</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE37">
         <v>8000</v>
@@ -4842,7 +4842,7 @@
         <v>82</v>
       </c>
       <c r="AD44">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE44">
         <v>8000</v>
@@ -4943,7 +4943,7 @@
         <v>82</v>
       </c>
       <c r="AD45">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE45">
         <v>8000</v>
@@ -5044,7 +5044,7 @@
         <v>82</v>
       </c>
       <c r="AD46">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE46">
         <v>8000</v>
@@ -5139,7 +5139,7 @@
         <v>82</v>
       </c>
       <c r="AD47">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE47">
         <v>8000</v>
@@ -5234,7 +5234,7 @@
         <v>82</v>
       </c>
       <c r="AD48">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE48">
         <v>8000</v>
@@ -5329,7 +5329,7 @@
         <v>82</v>
       </c>
       <c r="AD49">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE49">
         <v>8000</v>
@@ -5424,7 +5424,7 @@
         <v>82</v>
       </c>
       <c r="AD50">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE50">
         <v>8000</v>
@@ -5519,7 +5519,7 @@
         <v>82</v>
       </c>
       <c r="AD51">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE51">
         <v>8000</v>
@@ -5614,7 +5614,7 @@
         <v>82</v>
       </c>
       <c r="AD52">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE52">
         <v>8000</v>
@@ -5709,7 +5709,7 @@
         <v>82</v>
       </c>
       <c r="AD53">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE53">
         <v>8000</v>
@@ -5804,7 +5804,7 @@
         <v>82</v>
       </c>
       <c r="AD54">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE54">
         <v>8000</v>
@@ -5899,7 +5899,7 @@
         <v>82</v>
       </c>
       <c r="AD55">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE55">
         <v>8000</v>
@@ -5994,7 +5994,7 @@
         <v>82</v>
       </c>
       <c r="AD56">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE56">
         <v>8000</v>
@@ -6089,7 +6089,7 @@
         <v>82</v>
       </c>
       <c r="AD57">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE57">
         <v>8000</v>
@@ -6184,7 +6184,7 @@
         <v>82</v>
       </c>
       <c r="AD58">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE58">
         <v>8000</v>
@@ -6279,7 +6279,7 @@
         <v>82</v>
       </c>
       <c r="AD59">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE59">
         <v>8000</v>
@@ -6374,7 +6374,7 @@
         <v>82</v>
       </c>
       <c r="AD60">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE60">
         <v>8000</v>
@@ -7618,7 +7618,7 @@
         <v>82</v>
       </c>
       <c r="AD73">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE73">
         <v>8000</v>
@@ -7716,7 +7716,7 @@
         <v>82</v>
       </c>
       <c r="AD74">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE74">
         <v>8000</v>
@@ -7814,7 +7814,7 @@
         <v>82</v>
       </c>
       <c r="AD75">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE75">
         <v>8000</v>
@@ -7909,7 +7909,7 @@
         <v>82</v>
       </c>
       <c r="AD76">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE76">
         <v>8000</v>
@@ -8004,7 +8004,7 @@
         <v>82</v>
       </c>
       <c r="AD77">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE77">
         <v>8000</v>
@@ -8099,7 +8099,7 @@
         <v>82</v>
       </c>
       <c r="AD78">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE78">
         <v>8000</v>
@@ -8194,7 +8194,7 @@
         <v>82</v>
       </c>
       <c r="AD79">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE79">
         <v>8000</v>
@@ -8289,7 +8289,7 @@
         <v>82</v>
       </c>
       <c r="AD80">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE80">
         <v>8000</v>
@@ -8384,7 +8384,7 @@
         <v>82</v>
       </c>
       <c r="AD81">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE81">
         <v>8000</v>
@@ -8479,7 +8479,7 @@
         <v>82</v>
       </c>
       <c r="AD82">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE82">
         <v>8000</v>
@@ -8574,7 +8574,7 @@
         <v>82</v>
       </c>
       <c r="AD83">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE83">
         <v>8000</v>
@@ -8669,7 +8669,7 @@
         <v>82</v>
       </c>
       <c r="AD84">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE84">
         <v>8000</v>
@@ -8764,7 +8764,7 @@
         <v>82</v>
       </c>
       <c r="AD85">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE85">
         <v>8000</v>
@@ -8859,7 +8859,7 @@
         <v>82</v>
       </c>
       <c r="AD86">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE86">
         <v>8000</v>
@@ -8954,7 +8954,7 @@
         <v>82</v>
       </c>
       <c r="AD87">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE87">
         <v>8000</v>
@@ -9049,7 +9049,7 @@
         <v>82</v>
       </c>
       <c r="AD88">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE88">
         <v>8000</v>
@@ -9144,7 +9144,7 @@
         <v>82</v>
       </c>
       <c r="AD89">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE89">
         <v>8000</v>
@@ -9239,7 +9239,7 @@
         <v>82</v>
       </c>
       <c r="AD90">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE90">
         <v>8000</v>
@@ -9334,7 +9334,7 @@
         <v>82</v>
       </c>
       <c r="AD91">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE91">
         <v>8000</v>
@@ -9429,7 +9429,7 @@
         <v>82</v>
       </c>
       <c r="AD92">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE92">
         <v>8000</v>
@@ -9524,7 +9524,7 @@
         <v>82</v>
       </c>
       <c r="AD93">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE93">
         <v>8000</v>
@@ -9619,7 +9619,7 @@
         <v>82</v>
       </c>
       <c r="AD94">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE94">
         <v>8000</v>
@@ -9717,7 +9717,7 @@
         <v>82</v>
       </c>
       <c r="AD95">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE95">
         <v>8000</v>
@@ -9812,7 +9812,7 @@
         <v>82</v>
       </c>
       <c r="AD96">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE96">
         <v>8000</v>
@@ -9907,7 +9907,7 @@
         <v>82</v>
       </c>
       <c r="AD97">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE97">
         <v>8000</v>
@@ -10002,7 +10002,7 @@
         <v>82</v>
       </c>
       <c r="AD98">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE98">
         <v>8000</v>
@@ -10100,7 +10100,7 @@
         <v>82</v>
       </c>
       <c r="AD99">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE99">
         <v>8000</v>
@@ -10195,7 +10195,7 @@
         <v>82</v>
       </c>
       <c r="AD100">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE100">
         <v>8000</v>
@@ -10290,7 +10290,7 @@
         <v>82</v>
       </c>
       <c r="AD101">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE101">
         <v>8000</v>
@@ -10385,7 +10385,7 @@
         <v>82</v>
       </c>
       <c r="AD102">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE102">
         <v>8000</v>
@@ -10480,7 +10480,7 @@
         <v>82</v>
       </c>
       <c r="AD103">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE103">
         <v>8000</v>
@@ -10575,7 +10575,7 @@
         <v>82</v>
       </c>
       <c r="AD104">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE104">
         <v>8000</v>
@@ -10670,7 +10670,7 @@
         <v>82</v>
       </c>
       <c r="AD105">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE105">
         <v>8000</v>
@@ -10765,7 +10765,7 @@
         <v>82</v>
       </c>
       <c r="AD106">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE106">
         <v>8000</v>
@@ -10860,7 +10860,7 @@
         <v>82</v>
       </c>
       <c r="AD107">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE107">
         <v>8000</v>
@@ -10955,7 +10955,7 @@
         <v>82</v>
       </c>
       <c r="AD108">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE108">
         <v>8000</v>
@@ -11050,7 +11050,7 @@
         <v>82</v>
       </c>
       <c r="AD109">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE109">
         <v>8000</v>
@@ -11145,7 +11145,7 @@
         <v>82</v>
       </c>
       <c r="AD110">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE110">
         <v>8000</v>
@@ -11243,7 +11243,7 @@
         <v>82</v>
       </c>
       <c r="AD111">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE111">
         <v>8000</v>
@@ -11341,7 +11341,7 @@
         <v>82</v>
       </c>
       <c r="AD112">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE112">
         <v>8000</v>
@@ -11436,7 +11436,7 @@
         <v>82</v>
       </c>
       <c r="AD113">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE113">
         <v>8000</v>
@@ -11531,7 +11531,7 @@
         <v>82</v>
       </c>
       <c r="AD114">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="AE114">
         <v>8000</v>
